--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12383,17 +12383,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11657,7 +11657,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁北京</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,14 +12179,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -12058,22 +12058,22 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -12122,22 +12122,22 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -12319,17 +12319,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -11866,22 +11866,22 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,14 +11891,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
@@ -12218,22 +12218,22 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11839,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -11898,22 +11898,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,14 +11955,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,14 +12115,14 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12383,17 +12383,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,14 +11955,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,14 +12211,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,14 +11891,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -11908,12 +11908,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
@@ -11967,17 +11967,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,29 +12147,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11807,17 +11807,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
@@ -12095,17 +12095,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
@@ -12191,17 +12191,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11871,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,29 +11891,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -11935,17 +11935,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,14 +11955,14 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -11972,12 +11972,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,29 +11987,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,7 +12019,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12031,17 +12031,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,14 +12179,14 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
@@ -12255,17 +12255,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12378,22 +12378,22 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260713_vs_20260720.xlsx
@@ -11177,7 +11177,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -11802,22 +11802,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11827,29 +11827,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11859,29 +11859,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -11903,17 +11903,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11923,29 +11923,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11955,29 +11955,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -11999,17 +11999,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12019,29 +12019,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12063,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12083,29 +12083,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12115,29 +12115,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12159,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12179,29 +12179,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12211,29 +12211,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12243,29 +12243,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12346,22 +12346,22 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12383,17 +12383,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12410,22 +12410,22 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12474,22 +12474,22 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12499,29 +12499,29 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
